--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.1-8B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.1-8B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>187</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>404</v>
+        <v>191</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>191</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>410</v>
+        <v>175</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.1-8B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.1-8B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>191</v>
+        <v>141</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>175</v>
+        <v>232</v>
       </c>
       <c r="H3">
         <v>426</v>
